--- a/data/trans_orig/P44D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26124</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>35202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48343</t>
+          <t>47912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21915</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>38907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>52178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24050</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37192</t>
+          <t>37297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26748</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45292</t>
+          <t>45094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61259</t>
+          <t>61149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46731</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105198</t>
+          <t>104747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78482</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96463</t>
+          <t>97078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174988</t>
+          <t>173799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198254</t>
+          <t>198286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2016 (tasa de respuesta: 93,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,97 +2679,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>36545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30467</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37590</t>
+          <t>37737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48156</t>
+          <t>48451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27938</t>
+          <t>28009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36835</t>
+          <t>36608</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64057</t>
+          <t>63986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>80702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124505</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>143002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87776</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102213</t>
+          <t>102344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218177</t>
+          <t>218730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241362</t>
+          <t>241483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87133</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90752</t>
+          <t>90747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>96144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180358</t>
+          <t>181106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187877</t>
+          <t>188089</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356218</t>
+          <t>356079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>385907</t>
+          <t>385451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116273</t>
+          <t>115421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123409</t>
+          <t>123377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>478515</t>
+          <t>478469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509434</t>
+          <t>509577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83728</t>
+          <t>82926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97560</t>
+          <t>97294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58469</t>
+          <t>58624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66542</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145709</t>
+          <t>146484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162101</t>
+          <t>162457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33300</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>52055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158173</t>
+          <t>157852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173799</t>
+          <t>174135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160500</t>
+          <t>160069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171404</t>
+          <t>170869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322034</t>
+          <t>321691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342043</t>
+          <t>341950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83117</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>45666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113303</t>
+          <t>113496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>696046</t>
+          <t>696505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>757529</t>
+          <t>757430</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435534</t>
+          <t>435406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451549</t>
+          <t>451964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1145284</t>
+          <t>1145091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1212045</t>
+          <t>1212921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47912</t>
+          <t>48294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61460</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52178</t>
+          <t>51568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37297</t>
+          <t>37231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>44047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>61669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97078</t>
+          <t>97486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173799</t>
+          <t>173042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198286</t>
+          <t>198781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>36554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51037</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>63392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37737</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48451</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>36969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63986</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80702</t>
+          <t>80789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47632</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>124820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143002</t>
+          <t>143187</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>102259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218730</t>
+          <t>218851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241483</t>
+          <t>242348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -4734,27 +4734,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91220</t>
+          <t>100126</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>95947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94060</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90747</t>
+          <t>98966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96144</t>
+          <t>104621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>185280</t>
+          <t>202811</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181106</t>
+          <t>197629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188089</t>
+          <t>205611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>102195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>106458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>208654</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>208654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>208654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>17342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>26256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>377618</t>
+          <t>143442</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356079</t>
+          <t>136628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>385451</t>
+          <t>148442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>120396</t>
+          <t>133013</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115421</t>
+          <t>128094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123377</t>
+          <t>136352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>498014</t>
+          <t>276455</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>478469</t>
+          <t>268047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509577</t>
+          <t>282916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>386980</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>386980</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>386980</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>140333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>514164</t>
+          <t>294303</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>514164</t>
+          <t>294303</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>514164</t>
+          <t>294303</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91520</t>
+          <t>101013</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82926</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97294</t>
+          <t>107470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63242</t>
+          <t>74063</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58624</t>
+          <t>68743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>78167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>154762</t>
+          <t>175076</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146484</t>
+          <t>165284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162457</t>
+          <t>183315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107724</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107724</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107724</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>72306</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72306</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72306</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>180030</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>180030</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180030</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>22692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52055</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>166872</t>
+          <t>173045</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157852</t>
+          <t>164285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174135</t>
+          <t>181252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166444</t>
+          <t>181735</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160069</t>
+          <t>175433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170869</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>333317</t>
+          <t>354780</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321691</t>
+          <t>343224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341950</t>
+          <t>364100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>191473</t>
+          <t>198730</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>191473</t>
+          <t>198730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>191473</t>
+          <t>198730</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182272</t>
+          <t>198125</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182272</t>
+          <t>198125</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182272</t>
+          <t>198125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>373746</t>
+          <t>396855</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>373746</t>
+          <t>396855</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>373746</t>
+          <t>396855</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>70065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113496</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>727230</t>
+          <t>517627</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>696505</t>
+          <t>503935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>757430</t>
+          <t>530724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>444142</t>
+          <t>491496</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435406</t>
+          <t>480907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451964</t>
+          <t>499392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1171373</t>
+          <t>1009123</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1145091</t>
+          <t>993124</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1212921</t>
+          <t>1024126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
